--- a/pokemon_collection.xlsx
+++ b/pokemon_collection.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,6 +533,46 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>images/kabuto.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kabuto</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>50/62</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ken Sugimori</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>base3-50</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>images/kabuto.jpg</t>
         </is>
